--- a/artfynd/A 33434-2026 artfynd.xlsx
+++ b/artfynd/A 33434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137353533</v>
       </c>
       <c r="B2" t="n">
-        <v>92405</v>
+        <v>92408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137353539</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137356097</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>137356099</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137353534</v>
       </c>
       <c r="B6" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137353535</v>
       </c>
       <c r="B7" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137356101</v>
       </c>
       <c r="B8" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>137353530</v>
       </c>
       <c r="B9" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>137353540</v>
       </c>
       <c r="B10" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>137353528</v>
       </c>
       <c r="B11" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137353529</v>
       </c>
       <c r="B12" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>137353532</v>
       </c>
       <c r="B13" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>137356095</v>
       </c>
       <c r="B14" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>137353531</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>137356083</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>137356092</v>
       </c>
       <c r="B17" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>137353538</v>
       </c>
       <c r="B18" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>137356085</v>
       </c>
       <c r="B19" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>137356087</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>137353537</v>
       </c>
       <c r="B21" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>137353526</v>
       </c>
       <c r="B22" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 33434-2026 artfynd.xlsx
+++ b/artfynd/A 33434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137353533</v>
       </c>
       <c r="B2" t="n">
-        <v>92408</v>
+        <v>92410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137356097</v>
       </c>
       <c r="B4" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>137356099</v>
       </c>
       <c r="B5" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137353534</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137353535</v>
       </c>
       <c r="B7" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137356101</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>137353530</v>
       </c>
       <c r="B9" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>137353540</v>
       </c>
       <c r="B10" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33434-2026 artfynd.xlsx
+++ b/artfynd/A 33434-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137353533</v>
       </c>
       <c r="B2" t="n">
-        <v>92410</v>
+        <v>92415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137353539</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137356097</v>
       </c>
       <c r="B4" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>137356099</v>
       </c>
       <c r="B5" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137353534</v>
       </c>
       <c r="B6" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137353535</v>
       </c>
       <c r="B7" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137356101</v>
       </c>
       <c r="B8" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>137353530</v>
       </c>
       <c r="B9" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>137353540</v>
       </c>
       <c r="B10" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>137353528</v>
       </c>
       <c r="B11" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137353529</v>
       </c>
       <c r="B12" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>137353532</v>
       </c>
       <c r="B13" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>137356095</v>
       </c>
       <c r="B14" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>137353531</v>
       </c>
       <c r="B15" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>137356083</v>
       </c>
       <c r="B16" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>137356092</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>137353538</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>137356085</v>
       </c>
       <c r="B19" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>137356087</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>137353526</v>
       </c>
       <c r="B22" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
